--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/brand-360-report.md (agency HQ: campaigns/geo/YYYY-MM/&lt;brand&gt;/)</t>
+          <t>campaigns/geo/YYYY-MM/brand-360-report/</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/llm-buttons/ (see the skill)</t>
+          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -662,32 +662,32 @@
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Brand Optimisation</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-llm-buttons</t>
+          <t>mos-geo-ai-info</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
+          <t>AI Info Page: an official, sourced fact sheet for ChatGPT, Claude, Perplexity and Gemini (basic info, background, services, clients, methods, advantages, guidance for AI), with schema, a machine-readable JSON copy and a developer handover.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-llm-buttons</t>
+          <t>/mos-geo-ai-info</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
+          <t>campaigns/geo/YYYY-MM/ai-info/</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>AI Info Page, Initiatives</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -704,23 +704,51 @@
       <c r="K9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Content Strategy</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-llm-buttons</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-llm-buttons</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Initiatives</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="n"/>
       <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-llm-buttons: Client website URL</t>
-        </is>
-      </c>
+      <c r="B11" s="4" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -732,7 +760,11 @@
       <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="n"/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL</t>
+        </is>
+      </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
@@ -1421,6 +1453,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>AI Info Page: an official, sourced fact sheet for ChatGPT, Claude, Perplexity and Gemini (basic info, background, services, clients, methods, advantages, guidance for AI), with schema, a machine-readable JSON copy and a developer handover.</t>
+          <t>AI Info Page: an official, sourced fact sheet for ChatGPT, Claude, Perplexity and Gemini (basic info, background, services, clients, methods, advantages, guidance for AI), with one schema file and a developer handover.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -968,23 +968,51 @@
       <c r="K15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Brand Optimisation</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-google-preferred-sources</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Google 'Add as a preferred source' button: eligibility check, a button styled to the site using Google's official code, placement after the best paragraph, and a live verify. Readers who choose the site see it more in Top Stories and get a 'preferred' badge in AI Overviews and AI Mode.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-google-preferred-sources</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/preferred-sources/</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Initiatives</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="n"/>
       <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-dealbreakers: Client website URL (community or marketplace URLs optional); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+; mos-geo-fan-out-map: Gemini API key (free tier)</t>
-        </is>
-      </c>
+      <c r="B17" s="4" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
@@ -996,7 +1024,11 @@
       <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="n"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-dealbreakers: Client website URL (community or marketplace URLs optional); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+; mos-geo-fan-out-map: Gemini API key (free tier); mos-geo-google-preferred-sources: Client website URL (site code or WordPress access to install; otherwise a developer handover)</t>
+        </is>
+      </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
@@ -1619,6 +1651,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -748,23 +748,51 @@
       <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Brand Optimisation</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-google-preferred-sources</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Google 'Add as a preferred source' button: eligibility check, a button styled to the site using Google's official code, placement after the best paragraph, and a live verify. Readers who choose the site see it more in Top Stories and get a 'preferred' badge in AI Overviews and AI Mode.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-google-preferred-sources</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/preferred-sources/</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Initiatives</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n"/>
       <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL</t>
-        </is>
-      </c>
+      <c r="B12" s="4" t="n"/>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
@@ -776,7 +804,11 @@
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="n"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-google-preferred-sources: Client website URL (site code or WordPress access to install; otherwise a developer handover)</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -1454,6 +1486,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -748,43 +748,135 @@
       <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Technical Foundations</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-internal-links</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-internal-links</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>None yet (audit and recommendations live in the run folder)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n"/>
       <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Technical Foundations</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-schema-scraper</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Live JSON-LD snapshot of a URL list, rendered in a real browser so tag-manager and JavaScript schema is caught: one pure-JSON file per page ([] if none), sorted by page type. The 'before' state for a schema rebuild.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-schema-scraper</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/schema/</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>None yet (outputs live in the schema folder)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="n"/>
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Technical Foundations</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-schema-optimisation</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-schema-optimisation</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/schema/</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>None yet (outputs live in the schema folder)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="n"/>
       <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
@@ -800,7 +892,11 @@
       <c r="K14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Apify token (APIFY_TOKEN or `apify login`), a URL list; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV); Node 18+</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
@@ -1454,6 +1550,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Live JSON-LD snapshot of a URL list, rendered in a real browser so tag-manager and JavaScript schema is caught: one pure-JSON file per page ([] if none), sorted by page type. The 'before' state for a schema rebuild.</t>
+          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="15">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Apify token (APIFY_TOKEN or `apify login`), a URL list; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV); Node 18+</t>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -748,31 +748,91 @@
       <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Technical Foundations</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-internal-links</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-internal-links</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>None yet (audit and recommendations live in the run folder)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="n"/>
       <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Content Strategy</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-fan-out</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>For 1 to 500+ pages, finds the searches AI engines actually run (query fan-out) for the prompts each page should win, measures whether the page is cited today, and produces a per-page fix list (add exact string, add section, earn retrieval, skip unwinnable vendor searches) ranked by stability.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-fan-out</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/fan-out/</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Fan-Out, Initiatives</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="n"/>
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
@@ -788,7 +848,11 @@
       <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="n"/>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-fan-out: DataForSEO (LLM Responses + LLM Mentions)</t>
+        </is>
+      </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -1454,6 +1518,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K67"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
     <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -563,6 +564,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -799,7 +801,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-fan-out</t>
+          <t>mos-geo-query-fan-out</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -809,7 +811,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-fan-out</t>
+          <t>/mos-geo-query-fan-out</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -850,7 +852,7 @@
     <row r="14">
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-fan-out: DataForSEO (LLM Responses + LLM Mentions)</t>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-query-fan-out: DataForSEO (LLM Responses + LLM Mentions)</t>
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -1531,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J67"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1546,6 +1548,7 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1574,6 +1577,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -2513,7 +2517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M65"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2531,6 +2535,7 @@
     <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2545,6 +2550,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="B2:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,6 @@
     <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -564,7 +563,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -838,23 +836,51 @@
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Content Strategy</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-fan-out-map</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Free, inventory-wide companion to mos-geo-fan-out. Predicts each page's query fan-out with Gemini Flash (no search, no spend) from a sitemap or URL list, scores each page's own coverage, and maps which pages to optimise and which topics across the inventory have no page. Run first to prioritise before spending mos-geo-fan-out's DataForSEO budget.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-fan-out-map</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/mos-geo-fan-out-map/</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>None yet (report and per-page files live in the run folder)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="n"/>
       <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-query-fan-out: DataForSEO (LLM Responses + LLM Mentions)</t>
-        </is>
-      </c>
+      <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -866,7 +892,11 @@
       <c r="K14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-query-fan-out: DataForSEO (LLM Responses + LLM Mentions); mos-geo-fan-out-map: Gemini API key (free tier)</t>
+        </is>
+      </c>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
@@ -1522,6 +1552,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1533,7 +1564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="B2:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1548,7 +1579,6 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1577,7 +1607,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -2517,7 +2546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="B2:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2535,7 +2564,6 @@
     <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2550,7 +2578,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="32" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brand Truth Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Initiatives" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand Truth Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initiatives" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$B$7:$K$67</definedName>
@@ -711,27 +711,27 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-llm-buttons</t>
+          <t>mos-geo-dealbreakers</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
+          <t>Dealbreaker Detector: reads the brand's public site, community and reviews as a sceptical buyer and lists every reason a qualified buyer would walk away (proof, pricing, setup, maturity, risk, fit), each with a verified quote or the pages checked, plus priorities, what's already handled and an FAQ draft.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-llm-buttons</t>
+          <t>/mos-geo-dealbreakers</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
+          <t>campaigns/geo/YYYY-MM/dealbreakers/</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>Dealbreakers, Initiatives</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -750,32 +750,32 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Technical Foundations</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-internal-links</t>
+          <t>mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
+          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-internal-links</t>
+          <t>/mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
+          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>None yet (audit and recommendations live in the run folder)</t>
+          <t>Initiatives</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -799,27 +799,27 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-schema-scraper</t>
+          <t>mos-geo-internal-links</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
+          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-schema-scraper</t>
+          <t>/mos-geo-internal-links</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/schema/</t>
+          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>None yet (outputs live in the schema folder)</t>
+          <t>None yet (audit and recommendations live in the run folder)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-schema-optimisation</t>
+          <t>mos-geo-schema-scraper</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
+          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-schema-optimisation</t>
+          <t>/mos-geo-schema-scraper</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -880,23 +880,51 @@
       <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Technical Foundations</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-schema-optimisation</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-schema-optimisation</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/schema/</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>None yet (outputs live in the schema folder)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="n"/>
       <c r="K14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
-        </is>
-      </c>
+      <c r="B15" s="4" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
@@ -908,7 +936,11 @@
       <c r="K15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="n"/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-dealbreakers: Client website URL (community or marketplace URLs optional); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
+        </is>
+      </c>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
@@ -1553,6 +1585,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Free, inventory-wide companion to mos-geo-fan-out. Predicts each page's query fan-out with Gemini Flash (no search, no spend) from a sitemap or URL list, scores each page's own coverage, and maps which pages to optimise and which topics across the inventory have no page. Run first to prioritise before spending mos-geo-fan-out's DataForSEO budget.</t>
+          <t>Free, inventory-wide companion to mos-geo-query-fan-out. Predicts each page's query fan-out with Gemini Flash (no search, no spend) from a sitemap or URL list, scores each page's own coverage, and maps which pages to optimise and which topics across the inventory have no page. Run first to prioritise before spending mos-geo-query-fan-out's DataForSEO budget.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>None yet (report and per-page files live in the run folder)</t>
+          <t>Fan-Out Map, Initiatives</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand Truth Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initiatives" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Brand Truth Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Initiatives" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$B$7:$K$67</definedName>
@@ -924,23 +924,51 @@
       <c r="K14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Content Strategy</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-fan-out-map</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Free, inventory-wide query fan-out. Predicts each page's query fan-out with Gemini Flash (no search, no spend) from a sitemap or URL list, scores each page's own coverage, and maps which pages to optimise and which topics across the inventory have no page. Predicted, not observed - confirm priority pages with a live ChatGPT / Google AI Mode check before writing or optimising.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-fan-out-map</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/mos-geo-fan-out-map/</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Fan-Out Map, Initiatives</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n"/>
       <c r="K15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-dealbreakers: Client website URL (community or marketplace URLs optional); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
-        </is>
-      </c>
+      <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
@@ -952,7 +980,11 @@
       <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="n"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-dealbreakers: Client website URL (community or marketplace URLs optional); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+; mos-geo-fan-out-map: Gemini API key (free tier)</t>
+        </is>
+      </c>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
@@ -1586,6 +1618,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -706,32 +706,32 @@
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Brand Optimisation</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-llm-buttons</t>
+          <t>mos-geo-ai-info-generator</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
+          <t>Fast AI Info Page draft in the exact shape of Steve Toth's GPT, written from the brand's own brain, site crawl and a short interview; a lint gate fails any missing section or any number not in those inputs.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-llm-buttons</t>
+          <t>/mos-geo-ai-info-generator</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
+          <t>campaigns/geo/YYYY-MM/ai-info-draft/</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>None yet (page.md, page.html and handover.md live in the run folder)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -750,32 +750,32 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Technical Foundations</t>
+          <t>Brand Optimisation</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-internal-links</t>
+          <t>mos-geo-homepage-faqs</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
+          <t>12 to 20 homepage FAQs written for AI assistants to quote: one self-contained sentence per answer, entity first, every fact from the brand's own site, each linked to the internal page that backs it up, with FAQPage schema and a client approval tab.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-internal-links</t>
+          <t>/mos-geo-homepage-faqs</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
+          <t>campaigns/geo/YYYY-MM/homepage-faqs/</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>None yet (audit and recommendations live in the run folder)</t>
+          <t>Homepage FAQs, Initiatives</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -794,32 +794,32 @@
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Technical Foundations</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-schema-scraper</t>
+          <t>mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
+          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-schema-scraper</t>
+          <t>/mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/schema/</t>
+          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>None yet (outputs live in the schema folder)</t>
+          <t>Initiatives</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -843,27 +843,27 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-schema-optimisation</t>
+          <t>mos-geo-internal-links</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
+          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-schema-optimisation</t>
+          <t>/mos-geo-internal-links</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/schema/</t>
+          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>None yet (outputs live in the schema folder)</t>
+          <t>None yet (audit and recommendations live in the run folder)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -880,43 +880,135 @@
       <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Content Strategy</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-topic-clusters</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Keyword clusters (one cluster = one page) rolled up into topics with a pillar, each mapped to the page ranking today, with status (Owned, Striking, Cannibalised, Lost ...), opportunity score, home-page overload and a cannibalisation list; pairs judged by TypeSafe Jev, clusters and numbers built in code.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-topic-clusters</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/mos-geo-topic-clusters/</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>None yet (xlsx and README live in the run folder)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="n"/>
       <c r="K14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Technical Foundations</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-schema-scraper</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-schema-scraper</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/schema/</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>None yet (outputs live in the schema folder)</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n"/>
       <c r="K15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Technical Foundations</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-schema-optimisation</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-schema-optimisation</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/schema/</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>None yet (outputs live in the schema folder)</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="n"/>
       <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
@@ -932,7 +1024,11 @@
       <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="n"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-ai-info-generator: Brand website URL; a MarketingOS brain if there is one; mos-geo-homepage-faqs: Brand name and website URL; Scrapling recommended (uses AI Info Page and Brand 360 outputs when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-topic-clusters: Ahrefs Organic Keywords export or GSC page+query export; TypeSafe API key; OpenAI or Voyage key optional (embeddings); DataForSEO optional (SERP overlap); mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
+        </is>
+      </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
@@ -1553,6 +1649,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brand Truth Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Initiatives" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brand Truth Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initiatives" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$B$7:$K$67</definedName>
@@ -711,27 +711,27 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-ai-info-generator</t>
+          <t>mos-geo-homepage-faqs</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Fast AI Info Page draft in the exact shape of Steve Toth's GPT, written from the brand's own brain, site crawl and a short interview; a lint gate fails any missing section or any number not in those inputs.</t>
+          <t>Sourced, entity-first FAQs ranked for a homepage and FAQ page, with passage-level claim review, verified internal links where useful, matching FAQPage schema and a client approval tab; exports require current final lint.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-ai-info-generator</t>
+          <t>/mos-geo-homepage-faqs</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/ai-info-draft/</t>
+          <t>campaigns/geo/YYYY-MM/homepage-faqs/</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>None yet (page.md, page.html and handover.md live in the run folder)</t>
+          <t>Homepage FAQs, Initiatives</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -750,32 +750,32 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Brand Optimisation</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-homepage-faqs</t>
+          <t>mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>12 to 20 homepage FAQs written for AI assistants to quote: one self-contained sentence per answer, entity first, every fact from the brand's own site, each linked to the internal page that backs it up, with FAQPage schema and a client approval tab.</t>
+          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-homepage-faqs</t>
+          <t>/mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/homepage-faqs/</t>
+          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Homepage FAQs, Initiatives</t>
+          <t>Initiatives</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -794,32 +794,32 @@
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Technical Foundations</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-llm-buttons</t>
+          <t>mos-geo-internal-links</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
+          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-llm-buttons</t>
+          <t>/mos-geo-internal-links</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
+          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>None yet (audit and recommendations live in the run folder)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -838,32 +838,32 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Technical Foundations</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-internal-links</t>
+          <t>mos-geo-topic-clusters</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
+          <t>Keyword clusters (one cluster = one page) rolled up into topics with a pillar, each mapped to the page ranking today, with status (Owned, Striking, Cannibalised, Lost ...), opportunity score, home-page overload and a cannibalisation list; pairs judged by TypeSafe Jev, clusters and numbers built in code.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-internal-links</t>
+          <t>/mos-geo-topic-clusters</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
+          <t>campaigns/geo/YYYY-MM/mos-geo-topic-clusters/</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>None yet (audit and recommendations live in the run folder)</t>
+          <t>None yet (xlsx and README live in the run folder)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -882,32 +882,32 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Technical Foundations</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-topic-clusters</t>
+          <t>mos-geo-schema-scraper</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Keyword clusters (one cluster = one page) rolled up into topics with a pillar, each mapped to the page ranking today, with status (Owned, Striking, Cannibalised, Lost ...), opportunity score, home-page overload and a cannibalisation list; pairs judged by TypeSafe Jev, clusters and numbers built in code.</t>
+          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-topic-clusters</t>
+          <t>/mos-geo-schema-scraper</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/mos-geo-topic-clusters/</t>
+          <t>campaigns/geo/YYYY-MM/schema/</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>None yet (xlsx and README live in the run folder)</t>
+          <t>None yet (outputs live in the schema folder)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-schema-scraper</t>
+          <t>mos-geo-schema-optimisation</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
+          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-schema-scraper</t>
+          <t>/mos-geo-schema-optimisation</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -968,51 +968,23 @@
       <c r="K15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Technical Foundations</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>mos-geo-schema-optimisation</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>/mos-geo-schema-optimisation</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>campaigns/geo/YYYY-MM/schema/</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>None yet (outputs live in the schema folder)</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="n"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-homepage-faqs: Brand name and website URL; Python 3.10+, openpyxl for the workbook; whole mos-geo-skills pack (Scrapling optional); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-topic-clusters: Ahrefs Organic Keywords export or GSC page+query export; TypeSafe API key; OpenAI or Voyage key optional (embeddings); DataForSEO optional (SERP overlap); mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
+        </is>
+      </c>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
@@ -1024,11 +996,7 @@
       <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-ai-info-generator: Brand website URL; a MarketingOS brain if there is one; mos-geo-homepage-faqs: Brand name and website URL; Scrapling recommended (uses AI Info Page and Brand 360 outputs when present); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-topic-clusters: Ahrefs Organic Keywords export or GSC page+query export; TypeSafe API key; OpenAI or Voyage key optional (embeddings); DataForSEO optional (SERP overlap); mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+</t>
-        </is>
-      </c>
+      <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
@@ -1651,7 +1619,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Sourced, entity-first FAQs ranked for a homepage and FAQ page, with passage-level claim review, verified internal links where useful, matching FAQPage schema and a client approval tab; exports require current final lint.</t>
+          <t>Sourced FAQs in brand voice using existing buyer/Dealbreaker questions, with answer gaps retained, relevant page placement, passage-level review, verified internal links, matching FAQPage schema and client approval; exports require current final lint.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">

--- a/_shared/brand-audit/brand-audit-template.xlsx
+++ b/_shared/brand-audit/brand-audit-template.xlsx
@@ -750,32 +750,32 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Brand Optimisation</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-llm-buttons</t>
+          <t>mos-geo-review-sentiment</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
+          <t>Review sentiment audit: finds the brand's third-party review profiles (Trustpilot, Google Maps, ProductReview, G2, Capterra, Reddit and more), scrapes only the ones you pick, labels every review against an approved aspect taxonomy, and ranks the complaints to fix, with verbatim quotes, owners, a GEO action each, phrase word clouds and the unreplied 1 to 2 star reviews.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-llm-buttons</t>
+          <t>/mos-geo-review-sentiment</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
+          <t>campaigns/geo/YYYY-MM/review-sentiment/</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>Review Fixes, Initiatives</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -794,32 +794,32 @@
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Technical Foundations</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-internal-links</t>
+          <t>mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
+          <t>Client-ready LLM share buttons package: brief, code reference and an in-brand demo of 'ask ChatGPT / Claude / Perplexity about this page' buttons.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-internal-links</t>
+          <t>/mos-geo-llm-buttons</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
+          <t>campaigns/geo/YYYY-MM/llm-buttons/</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>None yet (audit and recommendations live in the run folder)</t>
+          <t>Initiatives</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -843,27 +843,27 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-schema-scraper</t>
+          <t>mos-geo-internal-links</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
+          <t>Internal link audit (true contextual links vs template noise, orphans, deep pages, links to redirects and errors, anchor conflicts) plus reviewable contextual link recommendations: target, sentence and verbatim anchor, judged by TypeSafe Jev.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-schema-scraper</t>
+          <t>/mos-geo-internal-links</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/schema/</t>
+          <t>campaigns/geo/YYYY-MM/mos-geo-internal-links/</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>None yet (outputs live in the schema folder)</t>
+          <t>None yet (audit and recommendations live in the run folder)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-schema-optimisation</t>
+          <t>mos-geo-schema-scraper</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
+          <t>Live JSON-LD snapshot of every page from a Screaming Frog crawl (custom extraction or stored HTML, JavaScript rendered): one pure-JSON file per page ([] if none), sorted by page type, broken blocks flagged. The 'before' state for a schema rebuild.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-schema-optimisation</t>
+          <t>/mos-geo-schema-scraper</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -926,32 +926,32 @@
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Technical Foundations</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-fan-out-map</t>
+          <t>mos-geo-schema-optimisation</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Free, inventory-wide query fan-out. Predicts each page's query fan-out with Gemini Flash (no search, no spend) from a sitemap or URL list, scores each page's own coverage, and maps which pages to optimise and which topics across the inventory have no page. Predicted, not observed - confirm priority pages with a live ChatGPT / Google AI Mode check before writing or optimising.</t>
+          <t>Landscape Word brief: current schema audit plus the 3 to 5 highest-impact schemas, each with a developer template and an example filled with the brand's real values, unverified values raised as margin comments.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-fan-out-map</t>
+          <t>/mos-geo-schema-optimisation</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/mos-geo-fan-out-map/</t>
+          <t>campaigns/geo/YYYY-MM/schema/</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Fan-Out Map, Initiatives</t>
+          <t>None yet (outputs live in the schema folder)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -970,32 +970,32 @@
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Brand Optimisation</t>
+          <t>Content Strategy</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>mos-geo-google-preferred-sources</t>
+          <t>mos-geo-fan-out-map</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Google 'Add as a preferred source' button: eligibility check, a button styled to the site using Google's official code, placement after the best paragraph, and a live verify. Readers who choose the site see it more in Top Stories and get a 'preferred' badge in AI Overviews and AI Mode.</t>
+          <t>Free, inventory-wide query fan-out. Predicts each page's query fan-out with Gemini Flash (no search, no spend) from a sitemap or URL list, scores each page's own coverage, and maps which pages to optimise and which topics across the inventory have no page. Predicted, not observed - confirm priority pages with a live ChatGPT / Google AI Mode check before writing or optimising.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>/mos-geo-google-preferred-sources</t>
+          <t>/mos-geo-fan-out-map</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>campaigns/geo/YYYY-MM/preferred-sources/</t>
+          <t>campaigns/geo/YYYY-MM/mos-geo-fan-out-map/</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Initiatives</t>
+          <t>Fan-Out Map, Initiatives</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1012,23 +1012,51 @@
       <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Brand Optimisation</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>mos-geo-google-preferred-sources</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Google 'Add as a preferred source' button: eligibility check, a button styled to the site using Google's official code, placement after the best paragraph, and a live verify. Readers who choose the site see it more in Top Stories and get a 'preferred' badge in AI Overviews and AI Mode.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>/mos-geo-google-preferred-sources</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>campaigns/geo/YYYY-MM/preferred-sources/</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Initiatives</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="n"/>
       <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-dealbreakers: Client website URL (community or marketplace URLs optional); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+; mos-geo-fan-out-map: Gemini API key (free tier); mos-geo-google-preferred-sources: Client website URL (site code or WordPress access to install; otherwise a developer handover)</t>
-        </is>
-      </c>
+      <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
@@ -1040,7 +1068,11 @@
       <c r="K18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Needs: mos-geo-brand-360: DataForSEO (OpenRouter, Bright Data optional); mos-geo-ai-info: Client website URL (uses Brand Truth Review corrections when present); mos-geo-dealbreakers: Client website URL (community or marketplace URLs optional); mos-geo-review-sentiment: Apify token (about $0.50 to $3 a run at 500 reviews per platform); TypeSafe API key optional (Claude labels in session without it); mos-geo-llm-buttons: Client website URL; mos-geo-internal-links: Screaming Frog Internal HTML + All Inlinks exports and stored HTML (GSC columns optional); TypeSafe API key for judge/place; mos-geo-schema-scraper: Screaming Frog crawl with JavaScript rendering and a JSON-LD custom extraction (or stored HTML); Apify token only for the paid fallback; mos-geo-schema-optimisation: Screaming Frog structured data export (CSV), ideally from the same crawl as the scraper; Node 18+; mos-geo-fan-out-map: Gemini API key (free tier); mos-geo-google-preferred-sources: Client website URL (site code or WordPress access to install; otherwise a developer handover)</t>
+        </is>
+      </c>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
@@ -1652,6 +1684,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
